--- a/data/result_Ulo_4core_full.xlsx
+++ b/data/result_Ulo_4core_full.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,6 +44,33 @@
     <t>UASWC_HI_Off</t>
   </si>
   <si>
+    <t>UASWC_HI_On</t>
+  </si>
+  <si>
+    <t>Fair_LO_Off</t>
+  </si>
+  <si>
+    <t>Fair_LO_On</t>
+  </si>
+  <si>
+    <t>Fair_HI_Off</t>
+  </si>
+  <si>
+    <t>Fair_HI_On</t>
+  </si>
+  <si>
+    <t>HUF_LO_Off</t>
+  </si>
+  <si>
+    <t>HUF_LO_On</t>
+  </si>
+  <si>
+    <t>HUF_HI_Off</t>
+  </si>
+  <si>
+    <t>HUF_HI_On</t>
+  </si>
+  <si>
     <t>LUF_LO_Off</t>
   </si>
   <si>
@@ -54,33 +81,6 @@
   </si>
   <si>
     <t>LUF_HI_On</t>
-  </si>
-  <si>
-    <t>UASWC_HI_On</t>
-  </si>
-  <si>
-    <t>Fair_LO_Off</t>
-  </si>
-  <si>
-    <t>Fair_LO_On</t>
-  </si>
-  <si>
-    <t>Fair_HI_Off</t>
-  </si>
-  <si>
-    <t>Fair_HI_On</t>
-  </si>
-  <si>
-    <t>HUF_LO_Off</t>
-  </si>
-  <si>
-    <t>HUF_LO_On</t>
-  </si>
-  <si>
-    <t>HUF_HI_Off</t>
-  </si>
-  <si>
-    <t>HUF_HI_On</t>
   </si>
 </sst>
 </file>
@@ -556,19 +556,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -577,7 +577,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -701,9 +701,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1050,8 +1049,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="18" width="12.625"/>
   </cols>
@@ -1113,59 +1112,59 @@
       </c>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>0.5</v>
       </c>
-      <c r="B2" s="1">
-        <v>0.500513027777778</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.99999983914086</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.999999916846436</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.999997337819703</v>
-      </c>
-      <c r="J2" s="1">
-        <v>0.999998406851479</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1">
-        <v>1</v>
-      </c>
-      <c r="M2" s="1">
-        <v>0.999993384749651</v>
-      </c>
-      <c r="N2" s="1">
-        <v>0.999996082984756</v>
-      </c>
-      <c r="O2" s="1">
-        <v>1</v>
-      </c>
-      <c r="P2" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>0.999997337819703</v>
-      </c>
-      <c r="R2" s="1">
-        <v>0.999998394372508</v>
+      <c r="B2">
+        <v>0.500179221470175</v>
+      </c>
+      <c r="C2">
+        <v>0.994375768130589</v>
+      </c>
+      <c r="D2">
+        <v>0.998017876052365</v>
+      </c>
+      <c r="E2">
+        <v>0.98485750307578</v>
+      </c>
+      <c r="F2">
+        <v>0.991524242258603</v>
+      </c>
+      <c r="G2">
+        <v>0.993622220344642</v>
+      </c>
+      <c r="H2">
+        <v>0.997716812865115</v>
+      </c>
+      <c r="I2">
+        <v>0.959254126367065</v>
+      </c>
+      <c r="J2">
+        <v>0.975035453743818</v>
+      </c>
+      <c r="K2">
+        <v>0.993333125310509</v>
+      </c>
+      <c r="L2">
+        <v>0.997571156827641</v>
+      </c>
+      <c r="M2">
+        <v>0.961692673356843</v>
+      </c>
+      <c r="N2">
+        <v>0.976934509352772</v>
+      </c>
+      <c r="O2">
+        <v>0.993953891577298</v>
+      </c>
+      <c r="P2">
+        <v>0.997860108769443</v>
+      </c>
+      <c r="Q2">
+        <v>0.980493381924772</v>
+      </c>
+      <c r="R2">
+        <v>0.988640265123969</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1173,55 +1172,55 @@
         <v>0.55</v>
       </c>
       <c r="B3">
-        <v>0.499569306547621</v>
+        <v>0.49895870652336</v>
       </c>
       <c r="C3">
-        <v>0.999993061568043</v>
+        <v>0.977756939042534</v>
       </c>
       <c r="D3">
-        <v>0.999997113752909</v>
+        <v>0.991762443238883</v>
       </c>
       <c r="E3">
-        <v>0.99995750224853</v>
+        <v>0.949699168547044</v>
       </c>
       <c r="F3">
-        <v>0.999981623483353</v>
+        <v>0.971015276886275</v>
       </c>
       <c r="G3">
-        <v>0.999992795029898</v>
+        <v>0.975550733922276</v>
       </c>
       <c r="H3">
-        <v>0.999939716775967</v>
+        <v>0.99089940414994</v>
       </c>
       <c r="I3">
-        <v>0.999968594817807</v>
+        <v>0.893906030454897</v>
       </c>
       <c r="J3">
-        <v>0.999979272638066</v>
+        <v>0.934932815154503</v>
       </c>
       <c r="K3">
-        <v>0.999980679818834</v>
+        <v>0.973988704135859</v>
       </c>
       <c r="L3">
-        <v>0.999992018773324</v>
+        <v>0.990145085480052</v>
       </c>
       <c r="M3">
-        <v>0.999776662144851</v>
+        <v>0.897918499834165</v>
       </c>
       <c r="N3">
-        <v>0.999865563524501</v>
+        <v>0.938197717824928</v>
       </c>
       <c r="O3">
-        <v>0.999991794494667</v>
+        <v>0.976729363973156</v>
       </c>
       <c r="P3">
-        <v>0.999996458497714</v>
+        <v>0.991331874883695</v>
       </c>
       <c r="Q3">
-        <v>0.999798291927402</v>
+        <v>0.939979011954213</v>
       </c>
       <c r="R3">
-        <v>0.999885200657039</v>
+        <v>0.964478211644308</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1229,55 +1228,55 @@
         <v>0.6</v>
       </c>
       <c r="B4">
-        <v>0.500069275776784</v>
+        <v>0.499019368869825</v>
       </c>
       <c r="C4">
-        <v>0.999968009493567</v>
+        <v>0.938957726132697</v>
       </c>
       <c r="D4">
-        <v>0.999986260927754</v>
+        <v>0.976611766588577</v>
       </c>
       <c r="E4">
-        <v>0.999644613986916</v>
+        <v>0.882259309889758</v>
       </c>
       <c r="F4">
-        <v>0.999961705630042</v>
+        <v>0.930614963125267</v>
       </c>
       <c r="G4">
-        <v>0.999983711182516</v>
+        <v>0.93289278800217</v>
       </c>
       <c r="H4">
-        <v>0.99925421047197</v>
+        <v>0.974188041977334</v>
       </c>
       <c r="I4">
-        <v>0.999591242067585</v>
+        <v>0.802444631860982</v>
       </c>
       <c r="J4">
-        <v>0.999829862790792</v>
+        <v>0.878824838136163</v>
       </c>
       <c r="K4">
-        <v>0.999941945385096</v>
+        <v>0.92964763263084</v>
       </c>
       <c r="L4">
-        <v>0.999975387868458</v>
+        <v>0.972432336984638</v>
       </c>
       <c r="M4">
-        <v>0.996733776048141</v>
+        <v>0.807190096035364</v>
       </c>
       <c r="N4">
-        <v>0.998044361793426</v>
+        <v>0.88294369347026</v>
       </c>
       <c r="O4">
-        <v>0.999909125456877</v>
+        <v>0.935495150563172</v>
       </c>
       <c r="P4">
-        <v>0.999959765157536</v>
+        <v>0.975133079434842</v>
       </c>
       <c r="Q4">
-        <v>0.997246960441736</v>
+        <v>0.868559914008407</v>
       </c>
       <c r="R4">
-        <v>0.998385399101258</v>
+        <v>0.921241201919064</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1285,55 +1284,55 @@
         <v>0.65</v>
       </c>
       <c r="B5">
-        <v>0.500456676020098</v>
+        <v>0.495976070504196</v>
       </c>
       <c r="C5">
-        <v>0.999340810034926</v>
+        <v>0.873489688672937</v>
       </c>
       <c r="D5">
-        <v>0.999727299320834</v>
+        <v>0.949521009718402</v>
       </c>
       <c r="E5">
-        <v>0.996600668294806</v>
+        <v>0.789755969408983</v>
       </c>
       <c r="F5">
-        <v>0.999259008175217</v>
+        <v>0.873325639851563</v>
       </c>
       <c r="G5">
-        <v>0.999692146042999</v>
+        <v>0.862380782534023</v>
       </c>
       <c r="H5">
-        <v>0.99415211584954</v>
+        <v>0.945017910614796</v>
       </c>
       <c r="I5">
-        <v>0.996704149913683</v>
+        <v>0.698612002432254</v>
       </c>
       <c r="J5">
-        <v>0.998223218725719</v>
+        <v>0.813951837527354</v>
       </c>
       <c r="K5">
-        <v>0.999091858227758</v>
+        <v>0.85675255128811</v>
       </c>
       <c r="L5">
-        <v>0.999619429948778</v>
+        <v>0.942097894452674</v>
       </c>
       <c r="M5">
-        <v>0.980861932296499</v>
+        <v>0.703540987040413</v>
       </c>
       <c r="N5">
-        <v>0.988489737467956</v>
+        <v>0.818127845391098</v>
       </c>
       <c r="O5">
-        <v>0.998791665286548</v>
+        <v>0.867907351327359</v>
       </c>
       <c r="P5">
-        <v>0.999462508205152</v>
+        <v>0.947096826147863</v>
       </c>
       <c r="Q5">
-        <v>0.982858475005318</v>
+        <v>0.773267657566036</v>
       </c>
       <c r="R5">
-        <v>0.989877466000919</v>
+        <v>0.861891616026427</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1341,55 +1340,55 @@
         <v>0.7</v>
       </c>
       <c r="B6">
-        <v>0.500231066537301</v>
+        <v>0.493403354206106</v>
       </c>
       <c r="C6">
-        <v>0.996076154120812</v>
+        <v>0.789499427909522</v>
       </c>
       <c r="D6">
-        <v>0.998353589033575</v>
+        <v>0.912587117897701</v>
       </c>
       <c r="E6">
-        <v>0.982865406662589</v>
+        <v>0.682936543139207</v>
       </c>
       <c r="F6">
-        <v>0.995189248113836</v>
+        <v>0.802896136164934</v>
       </c>
       <c r="G6">
-        <v>0.99793145396129</v>
+        <v>0.771109282604673</v>
       </c>
       <c r="H6">
-        <v>0.975155311324551</v>
+        <v>0.905118385901389</v>
       </c>
       <c r="I6">
-        <v>0.985829796463879</v>
+        <v>0.603293056823884</v>
       </c>
       <c r="J6">
-        <v>0.990728525258961</v>
+        <v>0.750939550648123</v>
       </c>
       <c r="K6">
-        <v>0.994170788061474</v>
+        <v>0.760638240327017</v>
       </c>
       <c r="L6">
-        <v>0.997483972411507</v>
+        <v>0.899696060196632</v>
       </c>
       <c r="M6">
-        <v>0.933998760155295</v>
+        <v>0.606344392006383</v>
       </c>
       <c r="N6">
-        <v>0.960342439432453</v>
+        <v>0.753839518515575</v>
       </c>
       <c r="O6">
-        <v>0.992766002425924</v>
+        <v>0.78011371548366</v>
       </c>
       <c r="P6">
-        <v>0.996705734822036</v>
+        <v>0.908546168557472</v>
       </c>
       <c r="Q6">
-        <v>0.938609802936013</v>
+        <v>0.668410616652729</v>
       </c>
       <c r="R6">
-        <v>0.963711784094354</v>
+        <v>0.792657662417571</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1397,55 +1396,55 @@
         <v>0.75</v>
       </c>
       <c r="B7">
-        <v>0.499589149961536</v>
+        <v>0.487133160281656</v>
       </c>
       <c r="C7">
-        <v>0.983429954567916</v>
+        <v>0.679617662375067</v>
       </c>
       <c r="D7">
-        <v>0.992647325538739</v>
+        <v>0.859733562445512</v>
       </c>
       <c r="E7">
-        <v>0.942059922705738</v>
+        <v>0.575836891044995</v>
       </c>
       <c r="F7">
-        <v>0.980051030160035</v>
+        <v>0.727131923571761</v>
       </c>
       <c r="G7">
-        <v>0.990984424731019</v>
+        <v>0.656607032855478</v>
       </c>
       <c r="H7">
-        <v>0.925547846154969</v>
+        <v>0.849236146964196</v>
       </c>
       <c r="I7">
-        <v>0.956573488571751</v>
+        <v>0.522922176876542</v>
       </c>
       <c r="J7">
-        <v>0.96737475902296</v>
+        <v>0.692197316564273</v>
       </c>
       <c r="K7">
-        <v>0.976096183627833</v>
+        <v>0.645210656285419</v>
       </c>
       <c r="L7">
-        <v>0.989214949586388</v>
+        <v>0.843270538800827</v>
       </c>
       <c r="M7">
-        <v>0.843364275953246</v>
+        <v>0.522925505253673</v>
       </c>
       <c r="N7">
-        <v>0.905436535045187</v>
+        <v>0.692000102224928</v>
       </c>
       <c r="O7">
-        <v>0.969868719914159</v>
+        <v>0.667659871002674</v>
       </c>
       <c r="P7">
-        <v>0.985745255530957</v>
+        <v>0.853835062124871</v>
       </c>
       <c r="Q7">
-        <v>0.851747937278331</v>
+        <v>0.567640095126622</v>
       </c>
       <c r="R7">
-        <v>0.911939852136636</v>
+        <v>0.720896570471846</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1453,167 +1452,55 @@
         <v>0.8</v>
       </c>
       <c r="B8">
-        <v>0.498713797746617</v>
+        <v>0.461030746831107</v>
       </c>
       <c r="C8">
-        <v>0.95074076540177</v>
+        <v>0.543382778403965</v>
       </c>
       <c r="D8">
-        <v>0.977316688135366</v>
+        <v>0.776143068960048</v>
       </c>
       <c r="E8">
-        <v>0.862799150752003</v>
+        <v>0.46019812421834</v>
       </c>
       <c r="F8">
-        <v>0.941334433699237</v>
+        <v>0.636014241078833</v>
       </c>
       <c r="G8">
-        <v>0.972598294710328</v>
+        <v>0.517369859702213</v>
       </c>
       <c r="H8">
-        <v>0.838054463034895</v>
+        <v>0.763368650070755</v>
       </c>
       <c r="I8">
-        <v>0.90384459412512</v>
+        <v>0.444570224781814</v>
       </c>
       <c r="J8">
-        <v>0.920400970450597</v>
+        <v>0.625188781368145</v>
       </c>
       <c r="K8">
-        <v>0.930634453712148</v>
+        <v>0.514754304856019</v>
       </c>
       <c r="L8">
-        <v>0.967718982114491</v>
+        <v>0.763299382521981</v>
       </c>
       <c r="M8">
-        <v>0.720325829433101</v>
+        <v>0.442378882493409</v>
       </c>
       <c r="N8">
-        <v>0.830423985548006</v>
+        <v>0.624396358319614</v>
       </c>
       <c r="O8">
-        <v>0.913379268503573</v>
+        <v>0.532254485163853</v>
       </c>
       <c r="P8">
-        <v>0.957968508914596</v>
+        <v>0.771644920297395</v>
       </c>
       <c r="Q8">
-        <v>0.730662607394823</v>
+        <v>0.459262411113451</v>
       </c>
       <c r="R8">
-        <v>0.838604518371767</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9">
-        <v>0.85</v>
-      </c>
-      <c r="B9">
-        <v>0.495982915870763</v>
-      </c>
-      <c r="C9">
-        <v>0.884233970798238</v>
-      </c>
-      <c r="D9">
-        <v>0.944666366559156</v>
-      </c>
-      <c r="E9">
-        <v>0.746436728856475</v>
-      </c>
-      <c r="F9">
-        <v>0.86601385070964</v>
-      </c>
-      <c r="G9">
-        <v>0.935242319696136</v>
-      </c>
-      <c r="H9">
-        <v>0.722387557717787</v>
-      </c>
-      <c r="I9">
-        <v>0.831617574367748</v>
-      </c>
-      <c r="J9">
-        <v>0.848322297296996</v>
-      </c>
-      <c r="K9">
-        <v>0.843914329013</v>
-      </c>
-      <c r="L9">
-        <v>0.925031283684048</v>
-      </c>
-      <c r="M9">
-        <v>0.600004178307343</v>
-      </c>
-      <c r="N9">
-        <v>0.754897639056338</v>
-      </c>
-      <c r="O9">
-        <v>0.812378299976549</v>
-      </c>
-      <c r="P9">
-        <v>0.906827783127891</v>
-      </c>
-      <c r="Q9">
-        <v>0.606741277425041</v>
-      </c>
-      <c r="R9">
-        <v>0.761209573046324</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:18">
-      <c r="A10">
-        <v>0.9</v>
-      </c>
-      <c r="B10">
-        <v>0.492188667594475</v>
-      </c>
-      <c r="C10">
-        <v>0.786194488911743</v>
-      </c>
-      <c r="D10">
-        <v>0.894020005461201</v>
-      </c>
-      <c r="E10">
-        <v>0.624980673787647</v>
-      </c>
-      <c r="F10">
-        <v>0.757429019684335</v>
-      </c>
-      <c r="G10">
-        <v>0.878357810449643</v>
-      </c>
-      <c r="H10">
-        <v>0.609408085876139</v>
-      </c>
-      <c r="I10">
-        <v>0.757834266053562</v>
-      </c>
-      <c r="J10">
-        <v>0.7692015020773</v>
-      </c>
-      <c r="K10">
-        <v>0.722762416741619</v>
-      </c>
-      <c r="L10">
-        <v>0.862104210826701</v>
-      </c>
-      <c r="M10">
-        <v>0.523605155853025</v>
-      </c>
-      <c r="N10">
-        <v>0.703096001441033</v>
-      </c>
-      <c r="O10">
-        <v>0.685424026870184</v>
-      </c>
-      <c r="P10">
-        <v>0.84011254615341</v>
-      </c>
-      <c r="Q10">
-        <v>0.525335518082679</v>
-      </c>
-      <c r="R10">
-        <v>0.705664224359323</v>
+        <v>0.634992252625618</v>
       </c>
     </row>
   </sheetData>
